--- a/样表模板.xlsx
+++ b/样表模板.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WPS Office\12.1.0.28505\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\WeChatProjects\miniprogram-1\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -46,7 +46,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="48"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -63,7 +63,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="48"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -77,7 +77,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="48"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -91,7 +91,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="48"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -108,7 +108,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="48"/>
+        <sz val="11"/>
         <rFont val="Arial Unicode MS"/>
         <charset val="134"/>
       </rPr>
@@ -117,7 +117,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="48"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
@@ -148,24 +148,24 @@
     </font>
     <font>
       <b/>
-      <sz val="48"/>
+      <sz val="11"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="48"/>
+      <sz val="11"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="48"/>
+      <sz val="11"/>
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="48"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -793,8 +793,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1368,169 +1371,169 @@
     <col min="40" max="40" width="46.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60.5" spans="1:40">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:40">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
     </row>
-    <row r="2" ht="122" spans="1:40">
-      <c r="A2" s="3" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:40">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="9">
         <v>1</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="9">
         <v>2</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="9">
         <v>3</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="9">
         <v>4</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="9">
         <v>5</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="9">
         <v>6</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="9">
         <v>7</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="9">
         <v>8</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="9">
         <v>9</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="9">
         <v>10</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="9">
         <v>11</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="9">
         <v>12</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="9">
         <v>13</v>
       </c>
-      <c r="T2" s="8">
+      <c r="T2" s="9">
         <v>14</v>
       </c>
-      <c r="U2" s="8">
+      <c r="U2" s="9">
         <v>15</v>
       </c>
-      <c r="V2" s="8">
+      <c r="V2" s="9">
         <v>16</v>
       </c>
-      <c r="W2" s="8">
+      <c r="W2" s="9">
         <v>17</v>
       </c>
-      <c r="X2" s="8">
+      <c r="X2" s="9">
         <v>18</v>
       </c>
-      <c r="Y2" s="8">
+      <c r="Y2" s="9">
         <v>19</v>
       </c>
-      <c r="Z2" s="8">
+      <c r="Z2" s="9">
         <v>20</v>
       </c>
-      <c r="AA2" s="8">
+      <c r="AA2" s="9">
         <v>21</v>
       </c>
-      <c r="AB2" s="8">
+      <c r="AB2" s="9">
         <v>22</v>
       </c>
-      <c r="AC2" s="8">
+      <c r="AC2" s="9">
         <v>23</v>
       </c>
-      <c r="AD2" s="8">
+      <c r="AD2" s="9">
         <v>24</v>
       </c>
-      <c r="AE2" s="8">
+      <c r="AE2" s="9">
         <v>25</v>
       </c>
-      <c r="AF2" s="8">
+      <c r="AF2" s="9">
         <v>26</v>
       </c>
-      <c r="AG2" s="8">
+      <c r="AG2" s="9">
         <v>27</v>
       </c>
-      <c r="AH2" s="8">
+      <c r="AH2" s="9">
         <v>28</v>
       </c>
-      <c r="AI2" s="8">
+      <c r="AI2" s="9">
         <v>29</v>
       </c>
-      <c r="AJ2" s="8">
+      <c r="AJ2" s="9">
         <v>30</v>
       </c>
-      <c r="AK2" s="8">
+      <c r="AK2" s="9">
         <v>31</v>
       </c>
-      <c r="AL2" s="9" t="s">
+      <c r="AL2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="AM2" s="9" t="s">
+      <c r="AM2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="AN2" s="10" t="s">
+      <c r="AN2" s="11" t="s">
         <v>9</v>
       </c>
     </row>

--- a/样表模板.xlsx
+++ b/样表模板.xlsx
@@ -41,6 +41,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
       <t>姓名</t>
     </r>
     <r>
@@ -58,6 +64,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
       <t>工种</t>
     </r>
     <r>
@@ -72,6 +84,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
       <t>备注（护照号码</t>
     </r>
     <r>
@@ -86,6 +104,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
       <t>单价</t>
     </r>
     <r>
@@ -103,6 +127,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -1358,17 +1388,17 @@
   <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="23.4545454545455" customWidth="1"/>
-    <col min="2" max="2" width="74" customWidth="1"/>
-    <col min="3" max="3" width="97.3636363636364" customWidth="1"/>
-    <col min="4" max="4" width="86.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="82.8181818181818" customWidth="1"/>
-    <col min="6" max="6" width="37.1818181818182" customWidth="1"/>
-    <col min="7" max="15" width="10.3636363636364" customWidth="1"/>
-    <col min="16" max="37" width="16.9090909090909" customWidth="1"/>
-    <col min="38" max="38" width="77.1818181818182" customWidth="1"/>
-    <col min="39" max="39" width="64.3636363636364" customWidth="1"/>
-    <col min="40" max="40" width="46.3636363636364" customWidth="1"/>
+    <col min="1" max="1" width="5.72727272727273" customWidth="1"/>
+    <col min="2" max="2" width="11.4545454545455" customWidth="1"/>
+    <col min="3" max="3" width="17.9090909090909" customWidth="1"/>
+    <col min="4" max="4" width="18.1818181818182" customWidth="1"/>
+    <col min="5" max="5" width="31.8181818181818" customWidth="1"/>
+    <col min="6" max="6" width="7.36363636363636" customWidth="1"/>
+    <col min="7" max="15" width="2.63636363636364" customWidth="1"/>
+    <col min="16" max="37" width="3.72727272727273" customWidth="1"/>
+    <col min="38" max="38" width="10.4545454545455" customWidth="1"/>
+    <col min="39" max="39" width="8.90909090909091" customWidth="1"/>
+    <col min="40" max="40" width="9.81818181818182" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:40">
